--- a/02_DIA_inicio_2026_analisis_assets/rbd_9706_escuela-bas-oscar-encalada-yovanovich_nt1_nucleos.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9706_escuela-bas-oscar-encalada-yovanovich_nt1_nucleos.xlsx
@@ -775,13 +775,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92B8CC1C-B39B-4B43-B9FB-9677743449A9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4709581E-00D0-48FB-BDC2-29F755CA2879}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE4CDD7E-45F0-41D1-9369-81DAF7BB08B4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2FF07681-56C6-42F8-B862-705F82CD8782}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B19013A8-3756-4074-A64D-6D6EB23B21C9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8299F62F-50D5-4FCB-921B-CCA510C85460}"/>
 </file>